--- a/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>n_configs</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>significant_holm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,10 +485,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8.924111948331683</v>
+        <v>13.07333682556324</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03031706165584091</v>
+        <v>0.004480664780706643</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -489,6 +499,12 @@
       <c r="H2" t="n">
         <v>4</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.04480664780706643</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,10 +523,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4582753824759</v>
+        <v>3.162731333758815</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6919332793876245</v>
+        <v>0.3672093050678141</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -521,6 +537,12 @@
       <c r="H3" t="n">
         <v>4</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.7344186101356281</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,10 +561,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.185789473684281</v>
+        <v>5.238317757009363</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06620597532277717</v>
+        <v>0.1551553072304037</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -553,6 +575,12 @@
       <c r="H4" t="n">
         <v>4</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.9309318433824225</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.347547974413644</v>
+        <v>5.374269005847764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5034732224372653</v>
+        <v>0.1463551373667468</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -585,6 +613,12 @@
       <c r="H5" t="n">
         <v>4</v>
       </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -603,10 +637,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.98854763144193</v>
+        <v>18.25515463917518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004661437408334961</v>
+        <v>0.0003896395492287</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -617,6 +651,12 @@
       <c r="H6" t="n">
         <v>4</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.0042860350415157</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -635,10 +675,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.180946291560232</v>
+        <v>4.819469026548434</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1590168507888242</v>
+        <v>0.1855039653793474</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -649,6 +689,12 @@
       <c r="H7" t="n">
         <v>4</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.7420158615173894</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -681,6 +727,12 @@
       <c r="H8" t="n">
         <v>3</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.4695408390427462</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -713,6 +765,12 @@
       <c r="H9" t="n">
         <v>3</v>
       </c>
+      <c r="I9" t="n">
+        <v>2.111757571790534e-07</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -745,6 +803,12 @@
       <c r="H10" t="n">
         <v>3</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.9217362553056075</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -777,6 +841,12 @@
       <c r="H11" t="n">
         <v>3</v>
       </c>
+      <c r="I11" t="n">
+        <v>0.5741033975581658</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -809,6 +879,12 @@
       <c r="H12" t="n">
         <v>3</v>
       </c>
+      <c r="I12" t="n">
+        <v>0.4597177557853582</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,6 +916,12 @@
       </c>
       <c r="H13" t="n">
         <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.06481540611642547</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,10 +500,10 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04480664780706643</v>
+        <v>0.06272930692989301</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7344186101356281</v>
+        <v>1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.238317757009363</v>
+        <v>12.81674208144804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1551553072304037</v>
+        <v>0.00505014669881191</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -576,7 +576,7 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9309318433824225</v>
+        <v>0.06565190708455483</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -590,7 +590,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.374269005847764</v>
+        <v>0.4588235294113474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1463551373667468</v>
+        <v>0.9278399656641164</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -614,7 +614,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.9278399656641164</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.25515463917518</v>
+        <v>5.238317757009363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003896395492287</v>
+        <v>0.1551553072304037</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -652,10 +652,10 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0042860350415157</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.819469026548434</v>
+        <v>5.374269005847764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1855039653793474</v>
+        <v>0.1463551373667468</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -690,7 +690,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7420158615173894</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -699,12 +699,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -713,36 +713,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.512000000000226</v>
+        <v>18.25515463917518</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4695408390427462</v>
+        <v>0.0003896395492287</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>195</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4695408390427462</v>
+        <v>0.005844593238430501</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -751,25 +751,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35.71096345514952</v>
+        <v>4.819469026548434</v>
       </c>
       <c r="E9" t="n">
-        <v>1.759797976492111e-08</v>
+        <v>0.1855039653793474</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>195</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.111757571790534e-07</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -780,7 +780,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.381868131868129</v>
+        <v>1.512000000000226</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1843472510611215</v>
+        <v>0.4695408390427462</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9217362553056075</v>
+        <v>0.9390816780854925</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -818,7 +818,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.307116104868614</v>
+        <v>35.71096345514952</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1913677991860552</v>
+        <v>1.759797976492111e-08</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -842,10 +842,10 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5741033975581658</v>
+        <v>2.815676762387378e-07</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -856,7 +856,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.713168187744563</v>
+        <v>3.305623471882236</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05746471947316978</v>
+        <v>0.1915106734389272</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -880,7 +880,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4597177557853582</v>
+        <v>0.7660426937557088</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.866873065015207</v>
+        <v>9.082644628098917</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007201711790713942</v>
+        <v>0.01065930228527278</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -918,9 +918,161 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06481540611642547</v>
+        <v>0.1172523251380006</v>
       </c>
       <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.381868131868129</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1843472510611215</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>195</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.307116104868614</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1913677991860552</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>195</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9568389959302761</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.713168187744563</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05746471947316978</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>195</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5746471947316978</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.866873065015207</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.007201711790713942</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>195</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0864205414885673</v>
+      </c>
+      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
